--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_55_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_55_R6.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0866</v>
+        <v>4.7035</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2499</v>
+        <v>2.4653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8367</v>
+        <v>2.2382</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7085</v>
+        <v>5.0923</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.073</v>
+        <v>4.6071</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7815</v>
+        <v>0.4852</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4265</v>
+        <v>4.1345</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7324000000000001</v>
+        <v>4.2215</v>
       </c>
       <c r="L2" t="n">
-        <v>4.159</v>
+        <v>-0.0871</v>
       </c>
       <c r="M2" t="n">
-        <v>0.282</v>
+        <v>0.9579</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3405</v>
+        <v>0.3856</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5723</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0876</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4955</v>
+        <v>0.2348</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0553</v>
+        <v>0.3462</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.1114</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.214</v>
+        <v>0.5361</v>
       </c>
       <c r="W2" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-1.214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7127</v>
+        <v>4.0433</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8441</v>
+        <v>3.2066</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8685</v>
+        <v>0.8367</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0923</v>
+        <v>3.7085</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6071</v>
+        <v>-1.073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4852</v>
+        <v>4.7815</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1345</v>
+        <v>3.4265</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2215</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0871</v>
+        <v>4.159</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9579</v>
+        <v>0.282</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3856</v>
+        <v>-0.3405</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5723</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.756</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.275</v>
+        <v>0.0121</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.481</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5361</v>
+        <v>-1.214</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5419</v>
+        <v>3.2393</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2714</v>
+        <v>3.6999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7294</v>
+        <v>-0.4606</v>
       </c>
       <c r="G4" t="n">
         <v>8.501899999999999</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2308</v>
+        <v>-1.5334</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8962</v>
+        <v>-0.4676</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.3346</v>
+        <v>-1.0657</v>
       </c>
       <c r="V4" t="n">
         <v>0.6778999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3031</v>
+        <v>1.3172</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3976</v>
+        <v>1.267</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9055</v>
+        <v>0.0502</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6289</v>
+        <v>0.4411</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4862</v>
+        <v>0.3374</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.1151</v>
+        <v>0.1038</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8362000000000001</v>
+        <v>0.0336</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3226</v>
+        <v>0.0336</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.1588</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2073</v>
+        <v>0.4075</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1636</v>
+        <v>0.3038</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0437</v>
+        <v>0.1038</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5377</v>
+        <v>0.1081</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3214</v>
+        <v>0.1612</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7837</v>
+        <v>-0.0532</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9304</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
         <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1486</v>
+        <v>0.0713</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0311</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1174</v>
+        <v>0.7039</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4411</v>
+        <v>-0.6289</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3374</v>
+        <v>2.4862</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1038</v>
+        <v>-3.1151</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0336</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0336</v>
+        <v>2.3226</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-3.1588</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4075</v>
+        <v>0.2073</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3038</v>
+        <v>0.1636</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1038</v>
+        <v>0.0437</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0606</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0747</v>
+        <v>0.2912</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0141</v>
+        <v>-0.9853</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>0.9304</v>
       </c>
       <c r="W6" t="n">
         <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2238</v>
+        <v>0.0367</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1287</v>
+        <v>-1.7002</v>
       </c>
       <c r="F7" t="n">
-        <v>1.905</v>
+        <v>1.7369</v>
       </c>
       <c r="G7" t="n">
         <v>0.4768</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0769</v>
+        <v>0.1836</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2003</v>
+        <v>0.2282</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1235</v>
+        <v>-0.0446</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4366</v>
+        <v>-0.2815</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.636</v>
+        <v>-2.7518</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1994</v>
+        <v>2.4703</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5359</v>
+        <v>-0.1208</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2102</v>
+        <v>0.6722</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7461</v>
+        <v>-0.793</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1854</v>
+        <v>-1.3433</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4537</v>
+        <v>-0.3963</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6391</v>
+        <v>-0.947</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3505</v>
+        <v>1.2225</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2435</v>
+        <v>1.0685</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.107</v>
+        <v>0.154</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2232</v>
+        <v>0.6073</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>0.3776</v>
       </c>
       <c r="U8" t="n">
-        <v>0.514</v>
+        <v>0.2298</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8197</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8197</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7773</v>
+        <v>-0.6382</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1803</v>
+        <v>-1.636</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4031</v>
+        <v>0.9977</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1208</v>
+        <v>-0.5359</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6722</v>
+        <v>0.2102</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.793</v>
+        <v>-0.7461</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3433</v>
+        <v>-0.1854</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3963</v>
+        <v>0.4537</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.947</v>
+        <v>-0.6391</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2225</v>
+        <v>-0.3505</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0685</v>
+        <v>-0.2435</v>
       </c>
       <c r="O9" t="n">
-        <v>0.154</v>
+        <v>-0.107</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1116</v>
+        <v>0.0215</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.051</v>
+        <v>-0.2908</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1625</v>
+        <v>0.3123</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5361</v>
+        <v>-0.8197</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1487</v>
+        <v>-1.5719</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5786</v>
+        <v>-0.901</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6304</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7859</v>
+        <v>0.3626</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9911</v>
+        <v>0.6686</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2051</v>
+        <v>-0.306</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3431</v>
+        <v>-3.3095</v>
       </c>
       <c r="E11" t="n">
         <v>-0.492</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.851</v>
+        <v>-2.8174</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2003</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3025</v>
+        <v>-1.2689</v>
       </c>
       <c r="T11" t="n">
         <v>-0.5975</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.6715</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.8634</v>
+        <v>7.610200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7785</v>
+        <v>2.525200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.0851</v>
+        <v>5.085</v>
       </c>
       <c r="G12" t="n">
         <v>15.1043</v>
@@ -1366,10 +1366,10 @@
         <v>12.9242</v>
       </c>
       <c r="K12" t="n">
-        <v>9.997400000000001</v>
+        <v>9.997399999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>2.926899999999999</v>
+        <v>2.926900000000001</v>
       </c>
       <c r="M12" t="n">
         <v>2.18</v>
@@ -1390,13 +1390,13 @@
         <v>12.7574</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2639</v>
+        <v>-2.5173</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.01770000000000016</v>
+        <v>0.7291999999999997</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.2463</v>
+        <v>-3.2465</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4976</v>
@@ -1405,13 +1405,13 @@
         <v>5.1085</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.6061</v>
+        <v>-6.606100000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0538</v>
+        <v>3.169</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6317</v>
+        <v>2.8516</v>
       </c>
       <c r="F13" t="n">
-        <v>0.422</v>
+        <v>0.3174</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4065</v>
+        <v>2.6315</v>
       </c>
       <c r="H13" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.7645</v>
       </c>
       <c r="I13" t="n">
-        <v>0.338</v>
+        <v>1.867</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5068</v>
+        <v>5.7272</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3228</v>
+        <v>2.6993</v>
       </c>
       <c r="L13" t="n">
-        <v>0.184</v>
+        <v>3.0279</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1003</v>
+        <v>-3.0957</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2543</v>
+        <v>-1.9348</v>
       </c>
       <c r="O13" t="n">
-        <v>0.154</v>
+        <v>-1.1609</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3917</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.7112</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3917</v>
+        <v>3.0154</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5777</v>
+        <v>0.5555</v>
       </c>
       <c r="T13" t="n">
-        <v>1.447</v>
+        <v>0.1577</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8694</v>
+        <v>0.3978</v>
       </c>
       <c r="V13" t="n">
         <v>0.6778999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5621</v>
+        <v>2.9352</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1439</v>
+        <v>1.8061</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4182</v>
+        <v>1.1291</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6315</v>
+        <v>0.4065</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7645</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.867</v>
+        <v>0.338</v>
       </c>
       <c r="J14" t="n">
-        <v>5.7272</v>
+        <v>0.5068</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6993</v>
+        <v>0.3228</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0279</v>
+        <v>0.184</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0957</v>
+        <v>-0.1003</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9348</v>
+        <v>-0.2543</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1609</v>
+        <v>0.154</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.7112</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0514</v>
+        <v>0.4591</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.55</v>
+        <v>0.6214</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4986</v>
+        <v>-0.1623</v>
       </c>
       <c r="V14" t="n">
         <v>0.6778999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5908</v>
+        <v>1.3047</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7983</v>
+        <v>0.0444</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2075</v>
+        <v>1.2603</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7606000000000001</v>
+        <v>0.7491</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3768</v>
+        <v>-1.138</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6162</v>
+        <v>1.8871</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7239</v>
+        <v>0.1739</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.7695</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3555</v>
+        <v>0.9435</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4845</v>
+        <v>0.5752</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7452</v>
+        <v>-0.3684</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.9436</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9055</v>
+        <v>-0.0707</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8758</v>
+        <v>-0.1296</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0297</v>
+        <v>0.0589</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1418</v>
+        <v>0.3943</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6083</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9903</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1363</v>
+        <v>0.0404</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.146</v>
+        <v>0.4793</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.8492</v>
+        <v>-0.3147</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8679</v>
+        <v>-0.4921</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.9813</v>
+        <v>0.1774</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.4149</v>
+        <v>0.1072</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5945</v>
+        <v>0.0336</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8204</v>
+        <v>0.0736</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4343</v>
+        <v>-0.422</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2734</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1609</v>
+        <v>0.1038</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7699</v>
+        <v>0.1386</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0331</v>
+        <v>-0.0668</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2631</v>
+        <v>0.2054</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7771</v>
+        <v>0.4836</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1916</v>
+        <v>0.1927</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9686</v>
+        <v>0.2909</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7491</v>
+        <v>-4.8492</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.138</v>
+        <v>-1.8679</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8871</v>
+        <v>-2.9813</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1739</v>
+        <v>-2.4149</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7695</v>
+        <v>-0.5945</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9435</v>
+        <v>-1.8204</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5752</v>
+        <v>-2.4343</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3684</v>
+        <v>-1.2734</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9436</v>
+        <v>-1.1609</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="Q17" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.5515</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.2632</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.0895</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.7501</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.7501</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.5983000000000001</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.3655</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.2328</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.3943</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.3943</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.306</v>
+        <v>0.0752</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0404</v>
+        <v>1.6188</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2656</v>
+        <v>-1.5436</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3147</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4921</v>
+        <v>-2.3768</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1774</v>
+        <v>1.6162</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1072</v>
+        <v>1.7239</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0336</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0736</v>
+        <v>2.3555</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.422</v>
+        <v>-2.4845</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-1.7452</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1038</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0751</v>
+        <v>1.3899</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0668</v>
+        <v>0.6963</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0083</v>
+        <v>0.6937</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6376</v>
+        <v>-1.155</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.792</v>
+        <v>-0.8484</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8456</v>
+        <v>-0.3066</v>
       </c>
       <c r="G19" t="n">
         <v>1.0238</v>
@@ -1936,13 +1936,13 @@
         <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1975</v>
+        <v>0.2851</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6484</v>
+        <v>0.2952</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5491</v>
+        <v>-0.0101</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.009</v>
+        <v>-2.7889</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0456</v>
+        <v>-2.9277</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0366</v>
+        <v>0.1387</v>
       </c>
       <c r="G20" t="n">
         <v>-5.3112</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5162</v>
+        <v>0.7363</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0193</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5355</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0.3943</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0688</v>
+        <v>-4.3497</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8169</v>
+        <v>-4.3451</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2519</v>
+        <v>-0.0045</v>
       </c>
       <c r="G21" t="n">
         <v>-4.2405</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.434</v>
+        <v>0.2851</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7389</v>
+        <v>-0.2671</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3049</v>
+        <v>0.5522</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3943</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.428</v>
+        <v>-4.6981</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9895</v>
+        <v>-3.5177</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4386</v>
+        <v>-1.1805</v>
       </c>
       <c r="G22" t="n">
         <v>-4.4389</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1489</v>
+        <v>0.581</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2794</v>
+        <v>0.7512</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4283</v>
+        <v>-0.1702</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.863300000000001</v>
+        <v>-4.504300000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.085000000000001</v>
+        <v>-5.0849</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7786</v>
+        <v>0.5804999999999996</v>
       </c>
       <c r="G23" t="n">
         <v>-15.1042</v>
@@ -2221,13 +2221,13 @@
         <v>-3.6641</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.18</v>
+        <v>-2.179999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>-1.4425</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7373999999999998</v>
+        <v>-0.7373999999999994</v>
       </c>
       <c r="M23" t="n">
         <v>-12.9242</v>
@@ -2248,13 +2248,13 @@
         <v>16.2368</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2641</v>
+        <v>5.623099999999999</v>
       </c>
       <c r="T23" t="n">
         <v>3.2464</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01770000000000005</v>
+        <v>2.3767</v>
       </c>
       <c r="V23" t="n">
         <v>1.4976</v>
@@ -2263,7 +2263,7 @@
         <v>6.6061</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.108500000000001</v>
+        <v>-5.108499999999999</v>
       </c>
     </row>
   </sheetData>
